--- a/Simulation/Results/p.mid_Censor.Ints_mean.surv.10.xlsx
+++ b/Simulation/Results/p.mid_Censor.Ints_mean.surv.10.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">mid</t>
   </si>
   <si>
-    <t xml:space="preserve">4 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5 mins</t>
+    <t xml:space="preserve">4.9 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5 mins</t>
   </si>
 </sst>
 </file>
@@ -419,13 +419,13 @@
         <v>50</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0384</v>
+        <v>0.0187</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0253</v>
+        <v>0.0066</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0233</v>
+        <v>0.0108</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
@@ -448,13 +448,13 @@
         <v>100</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0323</v>
+        <v>0.0231</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0091</v>
+        <v>0.0034</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0141</v>
+        <v>0.009</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
@@ -477,13 +477,13 @@
         <v>200</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0252</v>
+        <v>0.0221</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0009</v>
+        <v>0.0002</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0072</v>
+        <v>0.0042</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
@@ -506,13 +506,13 @@
         <v>500</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0241</v>
+        <v>0.0213</v>
       </c>
       <c r="C5" t="n">
         <v>0.0001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0013</v>
+        <v>0.0006</v>
       </c>
       <c r="E5" t="n">
         <v>0.1</v>
